--- a/Supplemental Files/Table S1.xlsx
+++ b/Supplemental Files/Table S1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CF8238-640E-470F-9213-7C8B5D26E1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B050D19E-0EA3-467A-8521-71CFDE3043B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,12 +30,6 @@
     <t>Dataset</t>
   </si>
   <si>
-    <t>upregulated</t>
-  </si>
-  <si>
-    <t>downregulated</t>
-  </si>
-  <si>
     <t>4DAGx24DAP</t>
   </si>
   <si>
@@ -54,7 +48,13 @@
     <t>4DAGxINF</t>
   </si>
   <si>
-    <t>TableS1 - Number of differential genes between each sample.</t>
+    <t>TableS2 - Number of long and short shifts identified between samples</t>
+  </si>
+  <si>
+    <t>short</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
 </sst>
 </file>
@@ -678,7 +678,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="13.5546875" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
@@ -689,7 +689,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -697,68 +697,68 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5">
-        <v>7902</v>
+        <v>618</v>
       </c>
       <c r="C3" s="5">
-        <v>9010</v>
+        <v>719</v>
       </c>
       <c r="D3" s="5">
-        <v>5560</v>
+        <v>602</v>
       </c>
       <c r="E3" s="2">
-        <v>6707</v>
+        <v>631</v>
       </c>
       <c r="F3" s="2">
-        <v>6414</v>
+        <v>597</v>
       </c>
       <c r="G3" s="2">
-        <v>9091</v>
+        <v>721</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5">
-        <v>3848</v>
+        <v>4939</v>
       </c>
       <c r="C4" s="5">
-        <v>5967</v>
+        <v>6816</v>
       </c>
       <c r="D4" s="5">
-        <v>6370</v>
+        <v>6347</v>
       </c>
       <c r="E4" s="6">
-        <v>5650</v>
+        <v>5706</v>
       </c>
       <c r="F4" s="6">
-        <v>6188</v>
+        <v>5156</v>
       </c>
       <c r="G4" s="6">
-        <v>5709</v>
+        <v>5393</v>
       </c>
     </row>
   </sheetData>

--- a/Supplemental Files/Table S1.xlsx
+++ b/Supplemental Files/Table S1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B050D19E-0EA3-467A-8521-71CFDE3043B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83BE9AF-9EA8-4FBF-98D1-90B5F9C42EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,20 +48,41 @@
     <t>4DAGxINF</t>
   </si>
   <si>
-    <t>TableS2 - Number of long and short shifts identified between samples</t>
-  </si>
-  <si>
     <t>short</t>
   </si>
   <si>
     <t>long</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TableS1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - Number of long and short shifts identified between samples</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,9 +91,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -170,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -178,6 +216,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -688,8 +727,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>7</v>
+      <c r="A1" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -717,7 +756,7 @@
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5">
         <v>618</v>
@@ -740,7 +779,7 @@
     </row>
     <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5">
         <v>4939</v>
@@ -762,7 +801,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/Supplemental Files/Table S1.xlsx
+++ b/Supplemental Files/Table S1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Desktop\2. Differencial analysis of barley promoterome\Supplement\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Šimon Pavlů\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83BE9AF-9EA8-4FBF-98D1-90B5F9C42EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F4E3B4-F39D-45AC-8473-003C6F3CB8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +58,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="238"/>
@@ -69,12 +68,23 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="238"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> - Number of long and short shifts identified between samples</t>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Number of long and short shifts identified between pairs of samples</t>
     </r>
   </si>
 </sst>
@@ -91,14 +101,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -107,7 +109,13 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -216,7 +224,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -801,10 +809,11 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Supplemental Files/Table S1.xlsx
+++ b/Supplemental Files/Table S1.xlsx
@@ -6,11 +6,11 @@
     <sheet state="visible" name="List1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_C0C2E084_8D73_4DB7_960C_BF9D6B0713AD_.wvu.FilterData">List1!$A$2:$G$4</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_C24529A1_A3D3_49BD_B085_88541129B54D_.wvu.FilterData">List1!$A$2:$G$4</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{C0C2E084-8D73-4DB7-960C-BF9D6B0713AD}" name="Tabulka1 filter view"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{C24529A1-A3D3-49BD-B085-88541129B54D}" name="Tabulka1 filter view"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -47,7 +47,7 @@
         <color theme="1"/>
         <sz val="11.0"/>
       </rPr>
-      <t>Number of long and short shifts identified between pairs of samples</t>
+      <t>Number of long and short promoter shifts identified between pairs of samples</t>
     </r>
   </si>
   <si>
@@ -133,7 +133,9 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1505,7 +1507,7 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{C0C2E084-8D73-4DB7-960C-BF9D6B0713AD}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{C24529A1-A3D3-49BD-B085-88541129B54D}" filter="1" showAutoFilter="1">
       <autoFilter ref="$A$2:$G$4"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
